--- a/originales/respuestas/2025/01. Calificadas/bucle p17/Alcaldía Local De Chapinero.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p17/Alcaldía Local De Chapinero.xlsx
@@ -9,7 +9,7 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="skJxYsjvQT+fNATgzkv8uz/LXXUSCqQhi2omB6lyL04="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="ktV5/9Wop2oamb3kqlpT2orm8SwHjnmkqKjgHkIiHIw="/>
     </ext>
   </extLst>
 </workbook>
@@ -314,7 +314,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="10.71"/>
-    <col customWidth="1" min="2" max="2" width="28.0"/>
+    <col customWidth="1" min="2" max="2" width="46.57"/>
     <col customWidth="1" min="3" max="26" width="10.71"/>
   </cols>
   <sheetData>
@@ -333,7 +333,7 @@
       </c>
       <c r="E1" s="1"/>
     </row>
-    <row r="2" ht="104.25" customHeight="1">
+    <row r="2" ht="252.0" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -351,6 +351,9 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
     </row>
+    <row r="3" ht="90.0" customHeight="1"/>
+    <row r="4" ht="90.0" customHeight="1"/>
+    <row r="5" ht="90.0" customHeight="1"/>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
     <row r="23" ht="15.75" customHeight="1"/>

--- a/originales/respuestas/2025/01. Calificadas/bucle p17/Alcaldía Local De Chapinero.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p17/Alcaldía Local De Chapinero.xlsx
@@ -46,12 +46,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <sz val="11.0"/>
@@ -61,7 +66,6 @@
     <font>
       <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -90,14 +94,17 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -322,34 +329,34 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1"/>
+      <c r="E1" s="2"/>
     </row>
     <row r="2" ht="252.0" customHeight="1">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
     </row>
     <row r="3" ht="90.0" customHeight="1"/>
     <row r="4" ht="90.0" customHeight="1"/>
